--- a/docs/weekly-mini-projects/weekly-mini-project-02/evaluation/Weekly_Mini_Project_02_Member_Leader_Feedback_Template.xlsx
+++ b/docs/weekly-mini-projects/weekly-mini-project-02/evaluation/Weekly_Mini_Project_02_Member_Leader_Feedback_Template.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nawarhisso/Documents/Training/BootCamp/repositories/b4f-cohort8-salamiyah-react-node-bootcamp-2026/docs/Weekly Mini Projects/weekly-mini-project-01/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Salem Jaza\Desktop\boot2\b4f-cohort8-salamiyah-next-nest-bootcamp-2026\docs\weekly-mini-projects\weekly-mini-project-02\evaluation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A9803A8-BD87-1040-A376-FB6AF3A7D7D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17955"/>
   </bookViews>
   <sheets>
     <sheet name="Leader Feedback" sheetId="1" r:id="rId1"/>
     <sheet name="Criteria Guide" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="65">
   <si>
     <t>Weekly Mini Project 02 — Member Feedback on Team Leader</t>
   </si>
@@ -219,17 +218,26 @@
   </si>
   <si>
     <t>Excellent</t>
+  </si>
+  <si>
+    <t>nagham jaza</t>
+  </si>
+  <si>
+    <t>yazan shartouh</t>
+  </si>
+  <si>
+    <t>he didn't know exactly how the  distribution would work ; he asked three people to work front-end but agree amongst themselves .this caused a bit of confusion</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -455,48 +463,48 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -798,12 +806,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -812,62 +820,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
     </row>
     <row r="2" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-    </row>
-    <row r="3" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="22" t="s">
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+    </row>
+    <row r="3" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-    </row>
-    <row r="6" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="25" t="s">
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+    </row>
+    <row r="6" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="29" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="21"/>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="32" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="21"/>
     </row>
-    <row r="7" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="25" t="s">
+    <row r="7" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="29" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="21"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="27"/>
-    </row>
-    <row r="8" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="25" t="s">
+      <c r="C7" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" s="23"/>
+    </row>
+    <row r="8" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="29" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="21"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="27"/>
+      <c r="C8" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="23"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
@@ -875,12 +887,12 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="33" t="s">
+      <c r="A11" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
@@ -903,7 +915,9 @@
       <c r="B14" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="6"/>
+      <c r="C14" s="6">
+        <v>5</v>
+      </c>
       <c r="D14" s="7"/>
     </row>
     <row r="15" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -913,7 +927,9 @@
       <c r="B15" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="8"/>
+      <c r="C15" s="8">
+        <v>5</v>
+      </c>
       <c r="D15" s="9"/>
     </row>
     <row r="16" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -923,8 +939,12 @@
       <c r="B16" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="7"/>
+      <c r="C16" s="6">
+        <v>4</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="17" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
@@ -933,7 +953,9 @@
       <c r="B17" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="8"/>
+      <c r="C17" s="8">
+        <v>5</v>
+      </c>
       <c r="D17" s="9"/>
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -943,7 +965,9 @@
       <c r="B18" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="6"/>
+      <c r="C18" s="6">
+        <v>5</v>
+      </c>
       <c r="D18" s="7"/>
     </row>
     <row r="19" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -953,7 +977,9 @@
       <c r="B19" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="8"/>
+      <c r="C19" s="8">
+        <v>5</v>
+      </c>
       <c r="D19" s="9"/>
     </row>
     <row r="20" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -963,7 +989,9 @@
       <c r="B20" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="6"/>
+      <c r="C20" s="6">
+        <v>5</v>
+      </c>
       <c r="D20" s="7"/>
     </row>
     <row r="21" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -973,7 +1001,9 @@
       <c r="B21" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="8"/>
+      <c r="C21" s="8">
+        <v>5</v>
+      </c>
       <c r="D21" s="9"/>
     </row>
     <row r="22" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -983,7 +1013,9 @@
       <c r="B22" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="6"/>
+      <c r="C22" s="6">
+        <v>5</v>
+      </c>
       <c r="D22" s="7"/>
     </row>
     <row r="23" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -993,7 +1025,9 @@
       <c r="B23" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="8"/>
+      <c r="C23" s="8">
+        <v>5</v>
+      </c>
       <c r="D23" s="9"/>
     </row>
     <row r="24" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -1003,7 +1037,9 @@
       <c r="B24" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="6"/>
+      <c r="C24" s="6">
+        <v>5</v>
+      </c>
       <c r="D24" s="7"/>
     </row>
     <row r="25" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -1013,7 +1049,9 @@
       <c r="B25" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="8"/>
+      <c r="C25" s="8">
+        <v>4</v>
+      </c>
       <c r="D25" s="9"/>
     </row>
     <row r="26" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -1023,7 +1061,9 @@
       <c r="B26" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="6"/>
+      <c r="C26" s="6">
+        <v>5</v>
+      </c>
       <c r="D26" s="7"/>
     </row>
     <row r="27" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -1033,7 +1073,9 @@
       <c r="B27" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="8"/>
+      <c r="C27" s="8">
+        <v>4</v>
+      </c>
       <c r="D27" s="9"/>
     </row>
     <row r="28" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -1043,7 +1085,9 @@
       <c r="B28" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="6"/>
+      <c r="C28" s="6">
+        <v>4</v>
+      </c>
       <c r="D28" s="7"/>
     </row>
     <row r="29" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -1053,7 +1097,9 @@
       <c r="B29" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="8"/>
+      <c r="C29" s="8">
+        <v>5</v>
+      </c>
       <c r="D29" s="9"/>
     </row>
     <row r="30" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -1063,71 +1109,64 @@
       <c r="B30" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C30" s="6"/>
+      <c r="C30" s="6">
+        <v>5</v>
+      </c>
       <c r="D30" s="7"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="32" t="s">
+      <c r="A31" s="31" t="s">
         <v>31</v>
       </c>
       <c r="B31" s="21"/>
-      <c r="C31" s="10" t="str">
+      <c r="C31" s="10">
         <f>IF(COUNT(C14:C30)=0,"",AVERAGE(C14:C30))</f>
-        <v/>
+        <v>4.7647058823529411</v>
       </c>
       <c r="D31" s="1"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="28" t="s">
+      <c r="A33" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="29"/>
-      <c r="C33" s="29"/>
+      <c r="B33" s="34"/>
+      <c r="C33" s="34"/>
       <c r="D33" s="21"/>
     </row>
-    <row r="34" spans="1:4" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="24" t="s">
+    <row r="34" spans="1:4" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="20" t="s">
         <v>33</v>
       </c>
       <c r="B34" s="21"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="27"/>
-    </row>
-    <row r="35" spans="1:4" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="24" t="s">
+      <c r="C34" s="24"/>
+      <c r="D34" s="23"/>
+    </row>
+    <row r="35" spans="1:4" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="20" t="s">
         <v>34</v>
       </c>
       <c r="B35" s="21"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="27"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="23"/>
     </row>
     <row r="36" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="24" t="s">
+      <c r="A36" s="20" t="s">
         <v>35</v>
       </c>
       <c r="B36" s="21"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="27"/>
-    </row>
-    <row r="37" spans="1:4" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="24" t="s">
+      <c r="C36" s="28"/>
+      <c r="D36" s="23"/>
+    </row>
+    <row r="37" spans="1:4" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="20" t="s">
         <v>36</v>
       </c>
       <c r="B37" s="21"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="27"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="C35:D35"/>
@@ -1140,12 +1179,21 @@
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C8:D8"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid rating" error="Please choose a rating from 1 to 5." promptTitle="Rating" prompt="1 Very Poor · 2 Needs Improvement · 3 Good · 4 Very Good · 5 Excellent" sqref="C14:C30" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid rating" error="Please choose a rating from 1 to 5." promptTitle="Rating" prompt="1 Very Poor · 2 Needs Improvement · 3 Good · 4 Very Good · 5 Excellent" sqref="C14:C30">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid answer" error="Please choose Yes, Mostly, or No." sqref="C36" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid answer" error="Please choose Yes, Mostly, or No." sqref="C36">
       <formula1>"Yes,Mostly,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1155,12 +1203,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -1168,32 +1216,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
     </row>
     <row r="2" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-    </row>
-    <row r="3" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="22" t="s">
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+    </row>
+    <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
     </row>
     <row r="4" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
@@ -1349,7 +1397,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="28" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A20" s="14">
         <v>14</v>
       </c>
@@ -1393,7 +1441,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="B25" s="17" t="s">
         <v>56</v>
       </c>

--- a/docs/weekly-mini-projects/weekly-mini-project-02/evaluation/Weekly_Mini_Project_02_Member_Leader_Feedback_Template.xlsx
+++ b/docs/weekly-mini-projects/weekly-mini-project-02/evaluation/Weekly_Mini_Project_02_Member_Leader_Feedback_Template.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Salem Jaza\Desktop\boot2\b4f-cohort8-salamiyah-next-nest-bootcamp-2026\docs\weekly-mini-projects\weekly-mini-project-02\evaluation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nawarhisso/Documents/Training/BootCamp/repositories/b4f-cohort8-salamiyah-react-node-bootcamp-2026/docs/Weekly Mini Projects/weekly-mini-project-01/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A9803A8-BD87-1040-A376-FB6AF3A7D7D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17955"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Leader Feedback" sheetId="1" r:id="rId1"/>
     <sheet name="Criteria Guide" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="62">
   <si>
     <t>Weekly Mini Project 02 — Member Feedback on Team Leader</t>
   </si>
@@ -218,26 +219,17 @@
   </si>
   <si>
     <t>Excellent</t>
-  </si>
-  <si>
-    <t>nagham jaza</t>
-  </si>
-  <si>
-    <t>yazan shartouh</t>
-  </si>
-  <si>
-    <t>he didn't know exactly how the  distribution would work ; he asked three people to work front-end but agree amongst themselves .this caused a bit of confusion</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -463,48 +455,48 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -806,12 +798,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D37"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -820,66 +812,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
     </row>
     <row r="2" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-    </row>
-    <row r="3" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="27" t="s">
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+    </row>
+    <row r="3" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-    </row>
-    <row r="6" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="29" t="s">
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+    </row>
+    <row r="6" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="25" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="21"/>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="20" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="21"/>
     </row>
-    <row r="7" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="29" t="s">
+    <row r="7" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="25" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="21"/>
-      <c r="C7" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" s="23"/>
-    </row>
-    <row r="8" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="29" t="s">
+      <c r="C7" s="30"/>
+      <c r="D7" s="27"/>
+    </row>
+    <row r="8" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="25" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="21"/>
-      <c r="C8" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" s="23"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="27"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
@@ -887,12 +875,12 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
@@ -915,9 +903,7 @@
       <c r="B14" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="6">
-        <v>5</v>
-      </c>
+      <c r="C14" s="6"/>
       <c r="D14" s="7"/>
     </row>
     <row r="15" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -927,9 +913,7 @@
       <c r="B15" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="8">
-        <v>5</v>
-      </c>
+      <c r="C15" s="8"/>
       <c r="D15" s="9"/>
     </row>
     <row r="16" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -939,12 +923,8 @@
       <c r="B16" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="6">
-        <v>4</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>64</v>
-      </c>
+      <c r="C16" s="6"/>
+      <c r="D16" s="7"/>
     </row>
     <row r="17" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
@@ -953,9 +933,7 @@
       <c r="B17" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="8">
-        <v>5</v>
-      </c>
+      <c r="C17" s="8"/>
       <c r="D17" s="9"/>
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -965,9 +943,7 @@
       <c r="B18" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="6">
-        <v>5</v>
-      </c>
+      <c r="C18" s="6"/>
       <c r="D18" s="7"/>
     </row>
     <row r="19" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -977,9 +953,7 @@
       <c r="B19" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="8">
-        <v>5</v>
-      </c>
+      <c r="C19" s="8"/>
       <c r="D19" s="9"/>
     </row>
     <row r="20" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -989,9 +963,7 @@
       <c r="B20" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="6">
-        <v>5</v>
-      </c>
+      <c r="C20" s="6"/>
       <c r="D20" s="7"/>
     </row>
     <row r="21" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -1001,9 +973,7 @@
       <c r="B21" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="8">
-        <v>5</v>
-      </c>
+      <c r="C21" s="8"/>
       <c r="D21" s="9"/>
     </row>
     <row r="22" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -1013,9 +983,7 @@
       <c r="B22" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="6">
-        <v>5</v>
-      </c>
+      <c r="C22" s="6"/>
       <c r="D22" s="7"/>
     </row>
     <row r="23" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -1025,9 +993,7 @@
       <c r="B23" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="8">
-        <v>5</v>
-      </c>
+      <c r="C23" s="8"/>
       <c r="D23" s="9"/>
     </row>
     <row r="24" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -1037,9 +1003,7 @@
       <c r="B24" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="6">
-        <v>5</v>
-      </c>
+      <c r="C24" s="6"/>
       <c r="D24" s="7"/>
     </row>
     <row r="25" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -1049,9 +1013,7 @@
       <c r="B25" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="8">
-        <v>4</v>
-      </c>
+      <c r="C25" s="8"/>
       <c r="D25" s="9"/>
     </row>
     <row r="26" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -1061,9 +1023,7 @@
       <c r="B26" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="6">
-        <v>5</v>
-      </c>
+      <c r="C26" s="6"/>
       <c r="D26" s="7"/>
     </row>
     <row r="27" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -1073,9 +1033,7 @@
       <c r="B27" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="8">
-        <v>4</v>
-      </c>
+      <c r="C27" s="8"/>
       <c r="D27" s="9"/>
     </row>
     <row r="28" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -1085,9 +1043,7 @@
       <c r="B28" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="6">
-        <v>4</v>
-      </c>
+      <c r="C28" s="6"/>
       <c r="D28" s="7"/>
     </row>
     <row r="29" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -1097,9 +1053,7 @@
       <c r="B29" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="8">
-        <v>5</v>
-      </c>
+      <c r="C29" s="8"/>
       <c r="D29" s="9"/>
     </row>
     <row r="30" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -1109,64 +1063,71 @@
       <c r="B30" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C30" s="6">
-        <v>5</v>
-      </c>
+      <c r="C30" s="6"/>
       <c r="D30" s="7"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="31" t="s">
+      <c r="A31" s="32" t="s">
         <v>31</v>
       </c>
       <c r="B31" s="21"/>
-      <c r="C31" s="10">
+      <c r="C31" s="10" t="str">
         <f>IF(COUNT(C14:C30)=0,"",AVERAGE(C14:C30))</f>
-        <v>4.7647058823529411</v>
+        <v/>
       </c>
       <c r="D31" s="1"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="33" t="s">
+      <c r="A33" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="34"/>
-      <c r="C33" s="34"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
       <c r="D33" s="21"/>
     </row>
-    <row r="34" spans="1:4" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="20" t="s">
+    <row r="34" spans="1:4" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="24" t="s">
         <v>33</v>
       </c>
       <c r="B34" s="21"/>
-      <c r="C34" s="24"/>
-      <c r="D34" s="23"/>
-    </row>
-    <row r="35" spans="1:4" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="20" t="s">
+      <c r="C34" s="26"/>
+      <c r="D34" s="27"/>
+    </row>
+    <row r="35" spans="1:4" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="24" t="s">
         <v>34</v>
       </c>
       <c r="B35" s="21"/>
-      <c r="C35" s="24"/>
-      <c r="D35" s="23"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="27"/>
     </row>
     <row r="36" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="20" t="s">
+      <c r="A36" s="24" t="s">
         <v>35</v>
       </c>
       <c r="B36" s="21"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="23"/>
-    </row>
-    <row r="37" spans="1:4" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="20" t="s">
+      <c r="C36" s="34"/>
+      <c r="D36" s="27"/>
+    </row>
+    <row r="37" spans="1:4" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="24" t="s">
         <v>36</v>
       </c>
       <c r="B37" s="21"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="23"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="C35:D35"/>
@@ -1179,21 +1140,12 @@
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C8:D8"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid rating" error="Please choose a rating from 1 to 5." promptTitle="Rating" prompt="1 Very Poor · 2 Needs Improvement · 3 Good · 4 Very Good · 5 Excellent" sqref="C14:C30">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid rating" error="Please choose a rating from 1 to 5." promptTitle="Rating" prompt="1 Very Poor · 2 Needs Improvement · 3 Good · 4 Very Good · 5 Excellent" sqref="C14:C30" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid answer" error="Please choose Yes, Mostly, or No." sqref="C36">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid answer" error="Please choose Yes, Mostly, or No." sqref="C36" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Yes,Mostly,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1203,12 +1155,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -1216,32 +1168,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
     </row>
     <row r="2" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-    </row>
-    <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="27" t="s">
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+    </row>
+    <row r="3" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
     </row>
     <row r="4" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
@@ -1397,7 +1349,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="28" x14ac:dyDescent="0.2">
       <c r="A20" s="14">
         <v>14</v>
       </c>
@@ -1441,7 +1393,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B25" s="17" t="s">
         <v>56</v>
       </c>
